--- a/VAVE Slide Files/VAVE-Slide-Input.xlsx
+++ b/VAVE Slide Files/VAVE-Slide-Input.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DG- 5Dr LT-Ph2 Tasks" sheetId="1" r:id="R2517d5ef133347b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DG- 5Dr LT-Ph2 Metadata" sheetId="2" r:id="R6fa52d9f75cd4444"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAVE-MB 2.0 Tasks" sheetId="3" r:id="Rf520aadce2c948bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAVE-MB 2.0 Metadata" sheetId="4" r:id="R56bec69d787340f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAVE-MB 2.0 VAVE Data" sheetId="5" r:id="R43601b54312b47d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cassette VAVE activities" sheetId="6" r:id="R024381cadc314d40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case VAVE activities" sheetId="7" r:id="Raaa6e538d82d4a5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAVE Slide Instructions" sheetId="8" r:id="Rcb89ed2561e84c78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DG- 5Dr LT-Ph2 Tasks" sheetId="1" r:id="Rc3503d57739e4cdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DG- 5Dr LT-Ph2 Metadata" sheetId="2" r:id="R693faaf874284608"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAVE-MB 2.0 Tasks" sheetId="3" r:id="Rc0b6d1a7754d4327"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAVE-MB 2.0 Metadata" sheetId="4" r:id="R78d2f54ec7634d82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAVE-MB 2.0 VAVE Data" sheetId="5" r:id="Raab6916aafca4a0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cassette VAVE activities" sheetId="6" r:id="R31bcf5791fa04313"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cassette VAVE activities (2)" sheetId="9" r:id="R4f802c9169b44feb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case VAVE activities" sheetId="7" r:id="R788ef3aa28264f05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAVE Slide Instructions" sheetId="8" r:id="R826baca557914906"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -26,7 +27,7 @@
     <x:numFmt numFmtId="166" formatCode="$#,##0.00"/>
     <x:numFmt numFmtId="167" formatCode="m/d/yyyy"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -88,8 +89,31 @@
       <x:color rgb="FF7F6000"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF202020"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF375623"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF202020"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF7F6000"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="14">
+  <x:fills count="88">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -156,6 +180,376 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFED7D31"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFA6A6A6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF70AD47"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFED7D31"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFA6A6A6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF70AD47"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFED7D31"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFA6A6A6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF70AD47"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFED7D31"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFA6A6A6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF70AD47"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFED7D31"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFA6A6A6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF70AD47"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFED7D31"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFA6A6A6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF70AD47"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFED7D31"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFA6A6A6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF70AD47"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="7">
     <x:border/>
@@ -217,7 +611,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="61">
+  <x:cellXfs count="501">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -359,6 +753,1140 @@
     <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="3" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="3" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="3" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="3" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="3" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="3" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="3" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="3" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="3" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="3" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="3" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="3" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="48" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="49" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="49" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="49" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="49" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="53" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="53" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="53" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="53" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="54" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="54" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="54" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="55" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="55" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="55" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="56" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="56" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="56" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="54" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="54" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="54" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="54" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="54" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="54" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="57" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="58" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="59" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="59" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="59" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="58" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="58" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="58" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="61" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="61" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="61" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="61" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="61" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="61" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="62" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="62" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="62" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="59" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="59" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="59" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="59" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="59" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="59" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="59" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="59" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="59" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="65" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="65" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="65" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="66" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="66" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="66" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="67" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="68" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="68" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="68" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="68" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="71" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="71" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="71" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="71" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="71" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="71" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="72" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="72" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="72" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="73" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="73" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="73" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="73" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="75" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="75" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="75" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="76" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="76" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="76" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="77" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="78" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="79" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="79" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="79" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="78" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="78" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="78" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="81" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="81" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="81" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="81" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="81" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="81" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="82" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="82" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="82" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="83" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="83" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="83" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="83" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="79" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="79" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="79" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="79" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="79" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="79" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="79" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="79" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="79" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="84" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="84" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="84" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="11" fillId="80" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="85" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="85" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="85" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="86" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="86" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="86" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="84" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="84" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="84" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="84" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="84" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="5" fillId="84" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="87" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -12664,1356 +14192,1280 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" customWidth="1"/>
-    <x:col min="2" max="2" width="12" customWidth="1"/>
-    <x:col min="3" max="3" width="34" customWidth="1"/>
-    <x:col min="4" max="4" width="8" customWidth="1"/>
-    <x:col min="5" max="5" width="10" customWidth="1"/>
-    <x:col min="6" max="6" width="12" customWidth="1"/>
-    <x:col min="7" max="7" width="11" customWidth="1"/>
-    <x:col min="8" max="8" width="48" customWidth="1"/>
-    <x:col min="9" max="9" width="13" customWidth="1"/>
-    <x:col min="10" max="10" width="13" customWidth="1"/>
-    <x:col min="11" max="11" width="13" customWidth="1"/>
-    <x:col min="12" max="12" width="15" customWidth="1"/>
-    <x:col min="13" max="13" width="13" customWidth="1"/>
-    <x:col min="14" max="14" width="16" customWidth="1"/>
-    <x:col min="15" max="15" width="16" customWidth="1"/>
-    <x:col min="16" max="16" width="38" customWidth="1"/>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="48" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="13" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="13" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="38" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Project</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Slide Order</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Slide Title</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Page</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Column</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Row On Page</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Task Order</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H1" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Task Name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I1" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential $</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J1" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Realized $</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K1" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savings</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L1" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savings Basis</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M1" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">End Date</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N1" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Status</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O1" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Include In Total</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P1" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Source Task ID</x:t>
-        </x:is>
+      <x:c r="A1" s="444" t="str">
+        <x:v>Project</x:v>
+      </x:c>
+      <x:c r="B1" s="444" t="str">
+        <x:v>Slide Order</x:v>
+      </x:c>
+      <x:c r="C1" s="444" t="str">
+        <x:v>Slide Title</x:v>
+      </x:c>
+      <x:c r="D1" s="444" t="str">
+        <x:v>Page</x:v>
+      </x:c>
+      <x:c r="E1" s="444" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="F1" s="444" t="str">
+        <x:v>Row On Page</x:v>
+      </x:c>
+      <x:c r="G1" s="444" t="str">
+        <x:v>Task Order</x:v>
+      </x:c>
+      <x:c r="H1" s="444" t="str">
+        <x:v>Task Name</x:v>
+      </x:c>
+      <x:c r="I1" s="444" t="str">
+        <x:v>Potential $</x:v>
+      </x:c>
+      <x:c r="J1" s="444" t="str">
+        <x:v>Realized $</x:v>
+      </x:c>
+      <x:c r="K1" s="444" t="str">
+        <x:v>Savings</x:v>
+      </x:c>
+      <x:c r="L1" s="444" t="str">
+        <x:v>Savings Basis</x:v>
+      </x:c>
+      <x:c r="M1" s="444" t="str">
+        <x:v>End Date</x:v>
+      </x:c>
+      <x:c r="N1" s="444" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="O1" s="444" t="str">
+        <x:v>Include In Total</x:v>
+      </x:c>
+      <x:c r="P1" s="444" t="str">
+        <x:v>Source Task ID</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="11" t="n">
+      <x:c r="A2" s="445" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B2" s="445" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cassette VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" s="11" t="n">
+      <x:c r="C2" s="445" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D2" s="445" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E2" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Left</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F2" s="11" t="n">
+      <x:c r="E2" s="445" t="str">
+        <x:v>Left</x:v>
+      </x:c>
+      <x:c r="F2" s="445" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G2" s="11" t="n">
+      <x:c r="G2" s="445" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H2" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CAP Tube testing - MT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I2" s="12" t="n">
+      <x:c r="H2" s="445" t="str">
+        <x:v>CAP Tube testing - MT</x:v>
+      </x:c>
+      <x:c r="I2" s="446" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="n"/>
-      <x:c r="K2" s="12" t="n">
+      <x:c r="J2" s="446"/>
+      <x:c r="K2" s="446" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="L2" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M2" s="13" t="n">
+      <x:c r="L2" s="445" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M2" s="447" t="n">
         <x:v>46276</x:v>
       </x:c>
-      <x:c r="N2" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O2" s="11" t="n">
+      <x:c r="N2" s="445" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="O2" s="445" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P2" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5949924d-b968-4ed3-b0c4-f3ead2566455</x:t>
-        </x:is>
+      <x:c r="P2" s="445" t="str">
+        <x:v>5949924d-b968-4ed3-b0c4-f3ead2566455</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="14" t="n">
+      <x:c r="A3" s="448" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B3" s="448" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C3" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cassette VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" s="14" t="n">
+      <x:c r="C3" s="448" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D3" s="448" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E3" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Left</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" s="14" t="n">
+      <x:c r="E3" s="448" t="str">
+        <x:v>Left</x:v>
+      </x:c>
+      <x:c r="F3" s="448" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G3" s="14" t="n">
+      <x:c r="G3" s="448" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H3" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Check valve removal</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I3" s="15" t="n">
+      <x:c r="H3" s="448" t="str">
+        <x:v>Check valve removal</x:v>
+      </x:c>
+      <x:c r="I3" s="449" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J3" s="15" t="n"/>
-      <x:c r="K3" s="15" t="n">
+      <x:c r="J3" s="449"/>
+      <x:c r="K3" s="449" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L3" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M3" s="16" t="n">
+      <x:c r="L3" s="448" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M3" s="450" t="n">
         <x:v>46248</x:v>
       </x:c>
-      <x:c r="N3" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O3" s="14" t="n">
+      <x:c r="N3" s="448" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="O3" s="448" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P3" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">8144df1b-b6d7-40ea-952e-a886b457c1bc</x:t>
-        </x:is>
+      <x:c r="P3" s="448" t="str">
+        <x:v>8144df1b-b6d7-40ea-952e-a886b457c1bc</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="11" t="n">
+      <x:c r="A4" s="445" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B4" s="445" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cassette VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="11" t="n">
+      <x:c r="C4" s="445" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D4" s="445" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Left</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" s="11" t="n">
+      <x:c r="E4" s="445" t="str">
+        <x:v>Left</x:v>
+      </x:c>
+      <x:c r="F4" s="445" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G4" s="11" t="n">
+      <x:c r="G4" s="445" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">S/M - 1 (Removing parts/clamps from design)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I4" s="12" t="n">
+      <x:c r="H4" s="445" t="str">
+        <x:v>S/M - 1 (Removing parts/clamps from design)</x:v>
+      </x:c>
+      <x:c r="I4" s="446" t="n">
         <x:v>7.5</x:v>
       </x:c>
-      <x:c r="J4" s="12" t="n"/>
-      <x:c r="K4" s="12" t="n">
+      <x:c r="J4" s="446"/>
+      <x:c r="K4" s="446" t="n">
         <x:v>7.5</x:v>
       </x:c>
-      <x:c r="L4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M4" s="13" t="n">
+      <x:c r="L4" s="445" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M4" s="447" t="n">
         <x:v>46237</x:v>
       </x:c>
-      <x:c r="N4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O4" s="11" t="n">
+      <x:c r="N4" s="445" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="O4" s="445" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">690cd47a-6343-424d-8bb7-e544b24bb00a</x:t>
-        </x:is>
+      <x:c r="P4" s="445" t="str">
+        <x:v>690cd47a-6343-424d-8bb7-e544b24bb00a</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="14" t="n">
+      <x:c r="A5" s="448" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B5" s="448" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cassette VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="14" t="n">
+      <x:c r="C5" s="448" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D5" s="448" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E5" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Left</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="14" t="n">
+      <x:c r="E5" s="448" t="str">
+        <x:v>Left</x:v>
+      </x:c>
+      <x:c r="F5" s="448" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G5" s="14" t="n">
+      <x:c r="G5" s="448" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H5" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">S/m - 2 (Control box redesign, evap shroud, compress base, cond. shroud)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I5" s="15" t="n">
+      <x:c r="H5" s="448" t="str">
+        <x:v>S/m - 2 (Control box redesign, evap shroud, compress base, cond. shroud)</x:v>
+      </x:c>
+      <x:c r="I5" s="449" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="J5" s="15" t="n"/>
-      <x:c r="K5" s="15" t="n">
+      <x:c r="J5" s="449"/>
+      <x:c r="K5" s="449" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="L5" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M5" s="16" t="n">
+      <x:c r="L5" s="448" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M5" s="450" t="n">
         <x:v>46316</x:v>
       </x:c>
-      <x:c r="N5" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O5" s="14" t="n">
+      <x:c r="N5" s="448" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="O5" s="448" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P5" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5658b013-55e3-4a2e-bb4b-9d23d4b12e0b</x:t>
-        </x:is>
+      <x:c r="P5" s="448" t="str">
+        <x:v>5658b013-55e3-4a2e-bb4b-9d23d4b12e0b</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="11" t="n">
+      <x:c r="A6" s="445" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B6" s="445" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cassette VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" s="11" t="n">
+      <x:c r="C6" s="445" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D6" s="445" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E6" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Left</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" s="11" t="n">
+      <x:c r="E6" s="445" t="str">
+        <x:v>Left</x:v>
+      </x:c>
+      <x:c r="F6" s="445" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="n">
+      <x:c r="G6" s="445" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H6" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">New enclosure for 2.0 (Molded foam/ Sm/ gasket)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I6" s="12" t="n">
+      <x:c r="H6" s="445" t="str">
+        <x:v>New enclosure for 2.0 (Molded foam/ Sm/ gasket)</x:v>
+      </x:c>
+      <x:c r="I6" s="446" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="J6" s="12" t="n"/>
-      <x:c r="K6" s="12" t="n">
+      <x:c r="J6" s="446"/>
+      <x:c r="K6" s="446" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="L6" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M6" s="13" t="n">
+      <x:c r="L6" s="445" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M6" s="447" t="n">
         <x:v>46325</x:v>
       </x:c>
-      <x:c r="N6" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O6" s="11" t="n">
+      <x:c r="N6" s="445" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="O6" s="445" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P6" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">68cf5939-3539-4efd-a155-97ef22fe5ae1</x:t>
-        </x:is>
+      <x:c r="P6" s="445" t="str">
+        <x:v>68cf5939-3539-4efd-a155-97ef22fe5ae1</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="14" t="n">
+      <x:c r="A7" s="448" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B7" s="448" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cassette VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" s="14" t="n">
+      <x:c r="C7" s="448" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D7" s="448" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Left</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F7" s="14" t="n">
+      <x:c r="E7" s="448" t="str">
+        <x:v>Right</x:v>
+      </x:c>
+      <x:c r="F7" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G7" s="448" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="n">
+      <x:c r="H7" s="448" t="str">
+        <x:v>Aluminum coil</x:v>
+      </x:c>
+      <x:c r="I7" s="449" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J7" s="449"/>
+      <x:c r="K7" s="449" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L7" s="448" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M7" s="450" t="n">
+        <x:v>46430</x:v>
+      </x:c>
+      <x:c r="N7" s="448" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="O7" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P7" s="448" t="str">
+        <x:v>1dbd22fd-e92f-4060-8ab5-5c5efb445f7f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="445" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B8" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="445" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D8" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="445" t="str">
+        <x:v>Right</x:v>
+      </x:c>
+      <x:c r="F8" s="445" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G8" s="445" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H8" s="445" t="str">
+        <x:v>Cheaper Carel controller</x:v>
+      </x:c>
+      <x:c r="I8" s="446" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J8" s="446"/>
+      <x:c r="K8" s="446" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L8" s="445" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M8" s="447" t="n">
+        <x:v>46272</x:v>
+      </x:c>
+      <x:c r="N8" s="445" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="O8" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P8" s="445" t="str">
+        <x:v>ba7b470f-08de-43b2-afe3-1684401a7fe8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="448" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B9" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="448" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D9" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" s="448" t="str">
+        <x:v>Right</x:v>
+      </x:c>
+      <x:c r="F9" s="448" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G9" s="448" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H9" s="448" t="str">
+        <x:v>Tube on drip tray</x:v>
+      </x:c>
+      <x:c r="I9" s="449" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="449"/>
+      <x:c r="K9" s="449" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L9" s="448" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M9" s="450" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="N9" s="448" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="O9" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P9" s="448" t="str">
+        <x:v>a6e8c12b-64e1-4ce1-81c8-092fa4b00e3f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="445" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B10" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="445" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D10" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E10" s="445" t="str">
+        <x:v>Right</x:v>
+      </x:c>
+      <x:c r="F10" s="445" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G10" s="445" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H10" s="445" t="str">
+        <x:v>Harness design</x:v>
+      </x:c>
+      <x:c r="I10" s="446" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J10" s="446"/>
+      <x:c r="K10" s="446" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L10" s="445" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M10" s="447" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="N10" s="445" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="O10" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P10" s="445" t="str">
+        <x:v>c6182a40-5c31-4b38-87b0-3e81c696f312</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="448" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B11" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="448" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D11" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E11" s="448" t="str">
+        <x:v>Right</x:v>
+      </x:c>
+      <x:c r="F11" s="448" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G11" s="448" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H11" s="448" t="str">
+        <x:v>Evap/ Condenser fan - 3 qty</x:v>
+      </x:c>
+      <x:c r="I11" s="449" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="J11" s="449"/>
+      <x:c r="K11" s="449" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L11" s="448" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M11" s="450" t="n">
+        <x:v>46283</x:v>
+      </x:c>
+      <x:c r="N11" s="448" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="O11" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P11" s="448" t="str">
+        <x:v>53d08d30-2db2-4c2b-9168-5338b53605d4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="445" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B12" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="445" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D12" s="445" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E12" s="445" t="str">
+        <x:v>Left</x:v>
+      </x:c>
+      <x:c r="F12" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G12" s="445" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H12" s="445" t="str">
+        <x:v>Pallet - CArdboard design</x:v>
+      </x:c>
+      <x:c r="I12" s="446" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J12" s="446"/>
+      <x:c r="K12" s="446" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L12" s="445" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M12" s="447" t="n">
+        <x:v>46307</x:v>
+      </x:c>
+      <x:c r="N12" s="445" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="O12" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P12" s="445" t="str">
+        <x:v>13f159e2-426e-4fc7-b2ea-e603c4e5eca6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="448" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B13" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C13" s="448" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D13" s="448" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E13" s="448" t="str">
+        <x:v>Left</x:v>
+      </x:c>
+      <x:c r="F13" s="448" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G13" s="448" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H13" s="448" t="str">
+        <x:v>Remove distributor from LT cassette</x:v>
+      </x:c>
+      <x:c r="I13" s="449"/>
+      <x:c r="J13" s="449"/>
+      <x:c r="K13" s="449" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="448" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M13" s="450" t="n">
+        <x:v>46308</x:v>
+      </x:c>
+      <x:c r="N13" s="448" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O13" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P13" s="448" t="str">
+        <x:v>f5812395-0ea5-4b0e-b6f2-acab96e589e3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="445" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B14" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="445" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D14" s="445" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E14" s="445" t="str">
+        <x:v>Left</x:v>
+      </x:c>
+      <x:c r="F14" s="445" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G14" s="445" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H14" s="445" t="str">
+        <x:v>New plastic base injection foam</x:v>
+      </x:c>
+      <x:c r="I14" s="446"/>
+      <x:c r="J14" s="446"/>
+      <x:c r="K14" s="446" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L14" s="445" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M14" s="447" t="n">
+        <x:v>46309</x:v>
+      </x:c>
+      <x:c r="N14" s="445" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O14" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P14" s="445" t="str">
+        <x:v>379ec39c-238b-4b54-8350-ef300bc80ffc</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="448" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B15" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C15" s="448" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D15" s="448" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E15" s="448" t="str">
+        <x:v>Left</x:v>
+      </x:c>
+      <x:c r="F15" s="448" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G15" s="448" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H15" s="448" t="str">
+        <x:v>New TXV Danfoss</x:v>
+      </x:c>
+      <x:c r="I15" s="449" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J15" s="449"/>
+      <x:c r="K15" s="449" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L15" s="448" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M15" s="450" t="n">
+        <x:v>46310</x:v>
+      </x:c>
+      <x:c r="N15" s="448" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O15" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P15" s="448" t="str">
+        <x:v>de24d2b8-7d7c-4143-880e-c0f1005e60ae</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="445" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B16" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C16" s="445" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D16" s="445" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E16" s="445" t="str">
+        <x:v>Left</x:v>
+      </x:c>
+      <x:c r="F16" s="445" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G16" s="445" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H16" s="445" t="str">
+        <x:v>New solenoid Sanhua</x:v>
+      </x:c>
+      <x:c r="I16" s="446" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J16" s="446"/>
+      <x:c r="K16" s="446" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L16" s="445" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M16" s="447" t="n">
+        <x:v>46311</x:v>
+      </x:c>
+      <x:c r="N16" s="445" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O16" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P16" s="445" t="str">
+        <x:v>3159e3c6-f12a-473a-ac75-b9bd59e3460e</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="448" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B17" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C17" s="448" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D17" s="448" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E17" s="448" t="str">
+        <x:v>Right</x:v>
+      </x:c>
+      <x:c r="F17" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" s="448" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H17" s="448" t="str">
+        <x:v>New HP Switch- Danfoss</x:v>
+      </x:c>
+      <x:c r="I17" s="449" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J17" s="449"/>
+      <x:c r="K17" s="449" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L17" s="448" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M17" s="450" t="n">
+        <x:v>46314</x:v>
+      </x:c>
+      <x:c r="N17" s="448" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O17" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P17" s="448" t="str">
+        <x:v>552e3bab-4309-4d1c-88ef-867e4947661d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="445" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B18" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C18" s="445" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D18" s="445" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E18" s="445" t="str">
+        <x:v>Right</x:v>
+      </x:c>
+      <x:c r="F18" s="445" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G18" s="445" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H18" s="445" t="str">
+        <x:v>Condenser coil with no quoting - Dunan</x:v>
+      </x:c>
+      <x:c r="I18" s="446"/>
+      <x:c r="J18" s="446"/>
+      <x:c r="K18" s="446" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L18" s="445" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M18" s="447" t="n">
+        <x:v>46315</x:v>
+      </x:c>
+      <x:c r="N18" s="445" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="O18" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P18" s="445" t="str">
+        <x:v>c932d38e-35da-4529-817e-f4add65b4234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="448" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B19" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C19" s="448" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D19" s="448" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E19" s="448" t="str">
+        <x:v>Right</x:v>
+      </x:c>
+      <x:c r="F19" s="448" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G19" s="448" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H19" s="448" t="str">
+        <x:v>Tariff - MT</x:v>
+      </x:c>
+      <x:c r="I19" s="449" t="n">
+        <x:v>43.7</x:v>
+      </x:c>
+      <x:c r="J19" s="449"/>
+      <x:c r="K19" s="449" t="n">
+        <x:v>43.7</x:v>
+      </x:c>
+      <x:c r="L19" s="448" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M19" s="450" t="n">
+        <x:v>46188</x:v>
+      </x:c>
+      <x:c r="N19" s="448" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="O19" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P19" s="448" t="str">
+        <x:v>5e7905c0-cd11-496d-b167-aee30805c055</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="445" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B20" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C20" s="445" t="str">
+        <x:v>Cassette VAVE activities</x:v>
+      </x:c>
+      <x:c r="D20" s="445" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E20" s="445" t="str">
+        <x:v>Right</x:v>
+      </x:c>
+      <x:c r="F20" s="445" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G20" s="445" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H20" s="445" t="str">
+        <x:v>Tariff - LT</x:v>
+      </x:c>
+      <x:c r="I20" s="446" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J20" s="446"/>
+      <x:c r="K20" s="446" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L20" s="445" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M20" s="447" t="n">
+        <x:v>46188</x:v>
+      </x:c>
+      <x:c r="N20" s="445" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="O20" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P20" s="445" t="str">
+        <x:v>a8f9342e-f798-40d2-a775-f70ad09e90f9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="448" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B21" s="448" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C21" s="448" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="D21" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E21" s="448" t="str">
+        <x:v>Full</x:v>
+      </x:c>
+      <x:c r="F21" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G21" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H21" s="448" t="str">
+        <x:v>Plastic Deck Pans</x:v>
+      </x:c>
+      <x:c r="I21" s="449" t="n">
+        <x:v>26.65</x:v>
+      </x:c>
+      <x:c r="J21" s="449"/>
+      <x:c r="K21" s="449" t="n">
+        <x:v>26.65</x:v>
+      </x:c>
+      <x:c r="L21" s="448" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M21" s="450" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="N21" s="448" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="O21" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P21" s="448" t="str">
+        <x:v>0666ca2c-efbd-410b-b618-091980be626a</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="445" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B22" s="445" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C22" s="445" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="D22" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22" s="445" t="str">
+        <x:v>Full</x:v>
+      </x:c>
+      <x:c r="F22" s="445" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G22" s="445" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H22" s="445" t="str">
+        <x:v>Simplify Raceway</x:v>
+      </x:c>
+      <x:c r="I22" s="446" t="n">
+        <x:v>3.07</x:v>
+      </x:c>
+      <x:c r="J22" s="446"/>
+      <x:c r="K22" s="446" t="n">
+        <x:v>3.07</x:v>
+      </x:c>
+      <x:c r="L22" s="445" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M22" s="447" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="N22" s="445" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="O22" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P22" s="445" t="str">
+        <x:v>c78076b0-ccd7-43e6-8c03-07c8cd138385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="448" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B23" s="448" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C23" s="448" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="D23" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E23" s="448" t="str">
+        <x:v>Full</x:v>
+      </x:c>
+      <x:c r="F23" s="448" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G23" s="448" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H23" s="448" t="str">
+        <x:v>Case power cord</x:v>
+      </x:c>
+      <x:c r="I23" s="449" t="n">
+        <x:v>5.5</x:v>
+      </x:c>
+      <x:c r="J23" s="449"/>
+      <x:c r="K23" s="449" t="n">
+        <x:v>5.5</x:v>
+      </x:c>
+      <x:c r="L23" s="448" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M23" s="450" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="N23" s="448" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="O23" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P23" s="448" t="str">
+        <x:v>4261a787-7843-4e5d-8577-381bfcd898af</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="445" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B24" s="445" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C24" s="445" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="D24" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E24" s="445" t="str">
+        <x:v>Full</x:v>
+      </x:c>
+      <x:c r="F24" s="445" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G24" s="445" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H24" s="445" t="str">
+        <x:v>10Amp Breaker</x:v>
+      </x:c>
+      <x:c r="I24" s="446" t="n">
+        <x:v>32.5</x:v>
+      </x:c>
+      <x:c r="J24" s="446"/>
+      <x:c r="K24" s="446" t="n">
+        <x:v>32.5</x:v>
+      </x:c>
+      <x:c r="L24" s="445" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M24" s="447" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="N24" s="445" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="O24" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P24" s="445" t="str">
+        <x:v>2f46503f-e39c-4618-b6b9-d5a91068ab8e</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="448" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B25" s="448" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C25" s="448" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="D25" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E25" s="448" t="str">
+        <x:v>Full</x:v>
+      </x:c>
+      <x:c r="F25" s="448" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G25" s="448" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H25" s="448" t="str">
+        <x:v>Simplify Under Door Support</x:v>
+      </x:c>
+      <x:c r="I25" s="449" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="J25" s="449"/>
+      <x:c r="K25" s="449" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="L25" s="448" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M25" s="450" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="N25" s="448" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="O25" s="448" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P25" s="448" t="str">
+        <x:v>6d086b43-5991-4599-8ce2-a0b5ff48a033</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="445" t="str">
+        <x:v>VAVE-MB 2.0</x:v>
+      </x:c>
+      <x:c r="B26" s="445" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C26" s="445" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="D26" s="445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26" s="445" t="str">
+        <x:v>Full</x:v>
+      </x:c>
+      <x:c r="F26" s="445" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Aluminum coil</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I7" s="15" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="J7" s="15" t="n"/>
-      <x:c r="K7" s="15" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="L7" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M7" s="16" t="n">
-        <x:v>46430</x:v>
-      </x:c>
-      <x:c r="N7" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O7" s="14" t="n">
+      <x:c r="G26" s="445" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H26" s="445" t="str">
+        <x:v>Reduce Qty of Canopy Foam Backers</x:v>
+      </x:c>
+      <x:c r="I26" s="446" t="n">
+        <x:v>5.3</x:v>
+      </x:c>
+      <x:c r="J26" s="446"/>
+      <x:c r="K26" s="446" t="n">
+        <x:v>5.3</x:v>
+      </x:c>
+      <x:c r="L26" s="445" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="M26" s="447" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="N26" s="445" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="O26" s="445" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P7" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1dbd22fd-e92f-4060-8ab5-5c5efb445f7f</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cassette VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Left</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F8" s="11" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H8" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cheaper Carel controller</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I8" s="12" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="J8" s="12" t="n"/>
-      <x:c r="K8" s="12" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L8" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M8" s="13" t="n">
-        <x:v>46272</x:v>
-      </x:c>
-      <x:c r="N8" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O8" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P8" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ba7b470f-08de-43b2-afe3-1684401a7fe8</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cassette VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Right</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F9" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H9" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tube on drip tray</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I9" s="15" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="n"/>
-      <x:c r="K9" s="15" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L9" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M9" s="16" t="n">
-        <x:v>46233</x:v>
-      </x:c>
-      <x:c r="N9" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O9" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P9" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">a6e8c12b-64e1-4ce1-81c8-092fa4b00e3f</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cassette VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Right</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F10" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G10" s="11" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H10" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Harness design</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I10" s="12" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="J10" s="12" t="n"/>
-      <x:c r="K10" s="12" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="L10" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M10" s="13" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="N10" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O10" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P10" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c6182a40-5c31-4b38-87b0-3e81c696f312</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cassette VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D11" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Right</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F11" s="14" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H11" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Evap/ Condenser fan - 3 qty</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I11" s="15" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n"/>
-      <x:c r="K11" s="15" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L11" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M11" s="16" t="n">
-        <x:v>46283</x:v>
-      </x:c>
-      <x:c r="N11" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O11" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P11" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">53d08d30-2db2-4c2b-9168-5338b53605d4</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cassette VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D12" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Right</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G12" s="11" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H12" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pallet - CArdboard design</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I12" s="12" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="J12" s="12" t="n"/>
-      <x:c r="K12" s="12" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L12" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M12" s="13" t="n">
-        <x:v>46307</x:v>
-      </x:c>
-      <x:c r="N12" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O12" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P12" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13f159e2-426e-4fc7-b2ea-e603c4e5eca6</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cassette VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Right</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" s="14" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="H13" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">New HP Switch- Danfoss</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I13" s="15" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n"/>
-      <x:c r="K13" s="15" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="L13" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M13" s="16" t="n">
-        <x:v>46314</x:v>
-      </x:c>
-      <x:c r="N13" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Started</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O13" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P13" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">552e3bab-4309-4d1c-88ef-867e4947661d</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cassette VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D14" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Right</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F14" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="H14" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tariff - MT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I14" s="12" t="n">
-        <x:v>43.7</x:v>
-      </x:c>
-      <x:c r="J14" s="12" t="n">
-        <x:v>43.7</x:v>
-      </x:c>
-      <x:c r="K14" s="12" t="n">
-        <x:v>43.7</x:v>
-      </x:c>
-      <x:c r="L14" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M14" s="13" t="n">
-        <x:v>46188</x:v>
-      </x:c>
-      <x:c r="N14" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Completed</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O14" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P14" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5e7905c0-cd11-496d-b167-aee30805c055</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cassette VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D15" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Right</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F15" s="14" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H15" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tariff - LT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I15" s="15" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K15" s="15" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L15" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M15" s="16" t="n">
-        <x:v>46188</x:v>
-      </x:c>
-      <x:c r="N15" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Completed</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O15" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P15" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">a8f9342e-f798-40d2-a775-f70ad09e90f9</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B16" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Case VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D16" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E16" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Full</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F16" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G16" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Plastic Deck Pans</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I16" s="12" t="n">
-        <x:v>26.65</x:v>
-      </x:c>
-      <x:c r="J16" s="12" t="n"/>
-      <x:c r="K16" s="12" t="n">
-        <x:v>26.65</x:v>
-      </x:c>
-      <x:c r="L16" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M16" s="13" t="n">
-        <x:v>46267</x:v>
-      </x:c>
-      <x:c r="N16" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O16" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P16" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0666ca2c-efbd-410b-b618-091980be626a</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B17" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Case VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D17" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Full</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F17" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H17" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Simplify Raceway</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I17" s="15" t="n">
-        <x:v>3.07</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="n"/>
-      <x:c r="K17" s="15" t="n">
-        <x:v>3.07</x:v>
-      </x:c>
-      <x:c r="L17" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M17" s="16" t="n">
-        <x:v>46241</x:v>
-      </x:c>
-      <x:c r="N17" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O17" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P17" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c78076b0-ccd7-43e6-8c03-07c8cd138385</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B18" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Case VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D18" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E18" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Full</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F18" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G18" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H18" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Case power cord</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I18" s="12" t="n">
-        <x:v>5.5</x:v>
-      </x:c>
-      <x:c r="J18" s="12" t="n"/>
-      <x:c r="K18" s="12" t="n">
-        <x:v>5.5</x:v>
-      </x:c>
-      <x:c r="L18" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M18" s="13" t="n">
-        <x:v>46266</x:v>
-      </x:c>
-      <x:c r="N18" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O18" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P18" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4261a787-7843-4e5d-8577-381bfcd898af</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B19" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Case VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D19" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Full</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F19" s="14" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H19" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10Amp Breaker</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I19" s="15" t="n">
-        <x:v>32.5</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="n"/>
-      <x:c r="K19" s="15" t="n">
-        <x:v>32.5</x:v>
-      </x:c>
-      <x:c r="L19" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M19" s="16" t="n">
-        <x:v>46245</x:v>
-      </x:c>
-      <x:c r="N19" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O19" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P19" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2f46503f-e39c-4618-b6b9-d5a91068ab8e</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B20" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Case VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D20" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Full</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F20" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G20" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H20" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Simplify Under Door Support</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I20" s="12" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="J20" s="12" t="n"/>
-      <x:c r="K20" s="12" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="L20" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M20" s="13" t="n">
-        <x:v>46241</x:v>
-      </x:c>
-      <x:c r="N20" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O20" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P20" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6d086b43-5991-4599-8ce2-a0b5ff48a033</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VAVE-MB 2.0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B21" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Case VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D21" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Full</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F21" s="14" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H21" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reduce Qty of Canopy Foam Backers</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I21" s="15" t="n">
-        <x:v>5.3</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="n"/>
-      <x:c r="K21" s="15" t="n">
-        <x:v>5.3</x:v>
-      </x:c>
-      <x:c r="L21" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Potential</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M21" s="16" t="n">
-        <x:v>46241</x:v>
-      </x:c>
-      <x:c r="N21" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O21" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P21" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">31928dcc-bb43-4ffa-8a8a-aba977f33410</x:t>
-        </x:is>
+      <x:c r="P26" s="445" t="str">
+        <x:v>31928dcc-bb43-4ffa-8a8a-aba977f33410</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
+  <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="N2:N250">
       <x:formula1>"On Track,Completed,Not Started,At Risk,On Hold"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="O2:O250">
+      <x:formula1>"1,0"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="N2:N26">
+      <x:formula1>"On Track,Completed,Not Started,At Risk,On Hold,REALIZED"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="O2:O26">
       <x:formula1>"1,0"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -14028,324 +15480,286 @@
   </x:sheetPr>
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="42" customWidth="1"/>
-    <x:col min="2" max="2" width="12" customWidth="1"/>
-    <x:col min="3" max="3" width="13" customWidth="1"/>
-    <x:col min="4" max="4" width="16" customWidth="1"/>
-    <x:col min="5" max="5" width="3" customWidth="1"/>
-    <x:col min="6" max="6" width="42" customWidth="1"/>
-    <x:col min="7" max="7" width="12" customWidth="1"/>
-    <x:col min="8" max="8" width="13" customWidth="1"/>
-    <x:col min="9" max="9" width="16" customWidth="1"/>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="3" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cassette VAVE activities</x:t>
-        </x:is>
+      <x:c r="A1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 1 of 2</x:v>
+      </x:c>
+      <x:c r="B1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 1 of 2</x:v>
+      </x:c>
+      <x:c r="C1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 1 of 2</x:v>
+      </x:c>
+      <x:c r="D1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 1 of 2</x:v>
+      </x:c>
+      <x:c r="E1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 1 of 2</x:v>
+      </x:c>
+      <x:c r="F1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 1 of 2</x:v>
+      </x:c>
+      <x:c r="G1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 1 of 2</x:v>
+      </x:c>
+      <x:c r="H1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 1 of 2</x:v>
+      </x:c>
+      <x:c r="I1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 1 of 2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="462" t="str">
+        <x:v>This section needs 2 pages — continues on tab "Cassette VAVE activities (2)".</x:v>
+      </x:c>
+      <x:c r="B2" s="462" t="str">
+        <x:v>This section needs 2 pages — continues on tab "Cassette VAVE activities (2)".</x:v>
+      </x:c>
+      <x:c r="C2" s="462" t="str">
+        <x:v>This section needs 2 pages — continues on tab "Cassette VAVE activities (2)".</x:v>
+      </x:c>
+      <x:c r="D2" s="462" t="str">
+        <x:v>This section needs 2 pages — continues on tab "Cassette VAVE activities (2)".</x:v>
+      </x:c>
+      <x:c r="E2" s="462" t="str">
+        <x:v>This section needs 2 pages — continues on tab "Cassette VAVE activities (2)".</x:v>
+      </x:c>
+      <x:c r="F2" s="462" t="str">
+        <x:v>This section needs 2 pages — continues on tab "Cassette VAVE activities (2)".</x:v>
+      </x:c>
+      <x:c r="G2" s="462" t="str">
+        <x:v>This section needs 2 pages — continues on tab "Cassette VAVE activities (2)".</x:v>
+      </x:c>
+      <x:c r="H2" s="462" t="str">
+        <x:v>This section needs 2 pages — continues on tab "Cassette VAVE activities (2)".</x:v>
+      </x:c>
+      <x:c r="I2" s="462" t="str">
+        <x:v>This section needs 2 pages — continues on tab "Cassette VAVE activities (2)".</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
-      <x:c r="A3" s="18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cassette VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H3" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Total:</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I3" s="20" t="n">
-        <x:f>SUMIFS('VAVE-MB 2.0 VAVE Data'!$K$2:$K$21,'VAVE-MB 2.0 VAVE Data'!$C$2:$C$21,"Cassette VAVE activities",'VAVE-MB 2.0 VAVE Data'!$O$2:$O$21,1)</x:f>
-        <x:v>268.2</x:v>
+      <x:c r="A3" s="456" t="str">
+        <x:v>Cassette VAVE activities · 1 of 2</x:v>
+      </x:c>
+      <x:c r="B3" s="456" t="str">
+        <x:v>Cassette VAVE activities · 1 of 2</x:v>
+      </x:c>
+      <x:c r="C3" s="456" t="str">
+        <x:v>Cassette VAVE activities · 1 of 2</x:v>
+      </x:c>
+      <x:c r="D3" s="456" t="str">
+        <x:v>Cassette VAVE activities · 1 of 2</x:v>
+      </x:c>
+      <x:c r="E3" s="456" t="str">
+        <x:v>Cassette VAVE activities · 1 of 2</x:v>
+      </x:c>
+      <x:c r="F3" s="456" t="str">
+        <x:v>Cassette VAVE activities · 1 of 2</x:v>
+      </x:c>
+      <x:c r="G3" s="456" t="str">
+        <x:v>Cassette VAVE activities · 1 of 2</x:v>
+      </x:c>
+      <x:c r="H3" s="457" t="str">
+        <x:v>Total:</x:v>
+      </x:c>
+      <x:c r="I3" s="459" t="n">
+        <x:f>SUMIFS('VAVE-MB 2.0 VAVE Data'!$K$2:$K$26,'VAVE-MB 2.0 VAVE Data'!$C$2:$C$26,"Cassette VAVE activities",'VAVE-MB 2.0 VAVE Data'!$O$2:$O$26,1)</x:f>
+        <x:v>283.2</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Task Name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savings</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">End</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Status</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Task Name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savings</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">End</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I5" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Status</x:t>
-        </x:is>
+      <x:c r="A5" s="465" t="str">
+        <x:v>Task Name</x:v>
+      </x:c>
+      <x:c r="B5" s="466" t="str">
+        <x:v>Savings</x:v>
+      </x:c>
+      <x:c r="C5" s="466" t="str">
+        <x:v>End</x:v>
+      </x:c>
+      <x:c r="D5" s="466" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="F5" s="465" t="str">
+        <x:v>Task Name</x:v>
+      </x:c>
+      <x:c r="G5" s="466" t="str">
+        <x:v>Savings</x:v>
+      </x:c>
+      <x:c r="H5" s="466" t="str">
+        <x:v>End</x:v>
+      </x:c>
+      <x:c r="I5" s="466" t="str">
+        <x:v>Status</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="39" customHeight="1">
-      <x:c r="A6" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CAP Tube testing - MT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="24" t="n">
+      <x:c r="A6" s="470" t="str">
+        <x:v>CAP Tube testing - MT</x:v>
+      </x:c>
+      <x:c r="B6" s="473" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C6" s="25" t="n">
+      <x:c r="C6" s="475" t="n">
         <x:v>46276</x:v>
       </x:c>
-      <x:c r="D6" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tube on drip tray</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G6" s="24" t="n">
+      <x:c r="D6" s="478" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="F6" s="470" t="str">
+        <x:v>Aluminum coil</x:v>
+      </x:c>
+      <x:c r="G6" s="473" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H6" s="475" t="n">
+        <x:v>46430</x:v>
+      </x:c>
+      <x:c r="I6" s="478" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="39" customHeight="1">
+      <x:c r="A7" s="482" t="str">
+        <x:v>Check valve removal</x:v>
+      </x:c>
+      <x:c r="B7" s="485" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C7" s="487" t="n">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="D7" s="478" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="F7" s="482" t="str">
+        <x:v>Cheaper Carel controller</x:v>
+      </x:c>
+      <x:c r="G7" s="485" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H7" s="487" t="n">
+        <x:v>46272</x:v>
+      </x:c>
+      <x:c r="I7" s="478" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="39" customHeight="1">
+      <x:c r="A8" s="470" t="str">
+        <x:v>S/M - 1 (Removing parts/clamps from design)</x:v>
+      </x:c>
+      <x:c r="B8" s="473" t="n">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="C8" s="475" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="D8" s="478" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="F8" s="470" t="str">
+        <x:v>Tube on drip tray</x:v>
+      </x:c>
+      <x:c r="G8" s="473" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H6" s="25" t="n">
+      <x:c r="H8" s="475" t="n">
         <x:v>46233</x:v>
       </x:c>
-      <x:c r="I6" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="39" customHeight="1">
-      <x:c r="A7" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Check valve removal</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="28" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="29" t="n">
-        <x:v>46248</x:v>
-      </x:c>
-      <x:c r="D7" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F7" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Harness design</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G7" s="28" t="n">
+      <x:c r="I8" s="478" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="39" customHeight="1">
+      <x:c r="A9" s="482" t="str">
+        <x:v>S/m - 2 (Control box redesign, evap shroud, compress base, cond. shroud)</x:v>
+      </x:c>
+      <x:c r="B9" s="485" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C9" s="487" t="n">
+        <x:v>46316</x:v>
+      </x:c>
+      <x:c r="D9" s="478" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="F9" s="482" t="str">
+        <x:v>Harness design</x:v>
+      </x:c>
+      <x:c r="G9" s="485" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H7" s="29" t="n">
+      <x:c r="H9" s="487" t="n">
         <x:v>46300</x:v>
       </x:c>
-      <x:c r="I7" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="39" customHeight="1">
-      <x:c r="A8" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">S/M - 1 (Removing parts/clamps from design)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="24" t="n">
-        <x:v>7.5</x:v>
-      </x:c>
-      <x:c r="C8" s="25" t="n">
-        <x:v>46237</x:v>
-      </x:c>
-      <x:c r="D8" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F8" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Evap/ Condenser fan - 3 qty</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G8" s="24" t="n">
+      <x:c r="I9" s="478" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="39" customHeight="1">
+      <x:c r="A10" s="470" t="str">
+        <x:v>New enclosure for 2.0 (Molded foam/ Sm/ gasket)</x:v>
+      </x:c>
+      <x:c r="B10" s="473" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C10" s="475" t="n">
+        <x:v>46325</x:v>
+      </x:c>
+      <x:c r="D10" s="478" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="F10" s="470" t="str">
+        <x:v>Evap/ Condenser fan - 3 qty</x:v>
+      </x:c>
+      <x:c r="G10" s="473" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H8" s="25" t="n">
+      <x:c r="H10" s="475" t="n">
         <x:v>46283</x:v>
       </x:c>
-      <x:c r="I8" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="39" customHeight="1">
-      <x:c r="A9" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">S/m - 2 (Control box redesign, evap shroud, compress base, cond. shroud)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="28" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C9" s="29" t="n">
-        <x:v>46316</x:v>
-      </x:c>
-      <x:c r="D9" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F9" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pallet - CArdboard design</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G9" s="28" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H9" s="29" t="n">
-        <x:v>46307</x:v>
-      </x:c>
-      <x:c r="I9" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="39" customHeight="1">
-      <x:c r="A10" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">New enclosure for 2.0 (Molded foam/ Sm/ gasket)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" s="24" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C10" s="25" t="n">
-        <x:v>46325</x:v>
-      </x:c>
-      <x:c r="D10" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F10" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">New HP Switch- Danfoss</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G10" s="24" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H10" s="25" t="n">
-        <x:v>46314</x:v>
-      </x:c>
-      <x:c r="I10" s="30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not Started</x:t>
-        </x:is>
+      <x:c r="I10" s="478" t="str">
+        <x:v>On Track</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="39" customHeight="1">
-      <x:c r="A11" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Aluminum coil</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="28" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C11" s="29" t="n">
-        <x:v>46430</x:v>
-      </x:c>
-      <x:c r="D11" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F11" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tariff - MT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G11" s="28" t="n">
-        <x:v>43.7</x:v>
-      </x:c>
-      <x:c r="H11" s="29" t="n">
-        <x:v>46188</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Completed</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A11"/>
+      <x:c r="B11"/>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
     </x:row>
     <x:row r="12" ht="39" customHeight="1">
-      <x:c r="A12" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cheaper Carel controller</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" s="24" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="n">
-        <x:v>46272</x:v>
-      </x:c>
-      <x:c r="D12" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tariff - LT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G12" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H12" s="25" t="n">
-        <x:v>46188</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Completed</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:I1"/>
     <x:mergeCell ref="A3:G3"/>
+    <x:mergeCell ref="A2:I2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -14353,212 +15767,498 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:tabColor rgb="00F47C20"/>
-  </x:sheetPr>
-  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="42" customWidth="1"/>
-    <x:col min="2" max="2" width="12" customWidth="1"/>
-    <x:col min="3" max="3" width="13" customWidth="1"/>
-    <x:col min="4" max="4" width="16" customWidth="1"/>
-    <x:col min="5" max="5" width="3" customWidth="1"/>
-    <x:col min="6" max="6" width="42" customWidth="1"/>
-    <x:col min="7" max="7" width="12" customWidth="1"/>
-    <x:col min="8" max="8" width="13" customWidth="1"/>
-    <x:col min="9" max="9" width="16" customWidth="1"/>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="3" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Case VAVE activities</x:t>
-        </x:is>
+      <x:c r="A1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 2 of 2</x:v>
+      </x:c>
+      <x:c r="B1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 2 of 2</x:v>
+      </x:c>
+      <x:c r="C1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 2 of 2</x:v>
+      </x:c>
+      <x:c r="D1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 2 of 2</x:v>
+      </x:c>
+      <x:c r="E1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 2 of 2</x:v>
+      </x:c>
+      <x:c r="F1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 2 of 2</x:v>
+      </x:c>
+      <x:c r="G1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 2 of 2</x:v>
+      </x:c>
+      <x:c r="H1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 2 of 2</x:v>
+      </x:c>
+      <x:c r="I1" s="453" t="str">
+        <x:v>Cassette VAVE activities · 2 of 2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="462" t="str">
+        <x:v>This section needs 2 pages — continued from tab "Cassette VAVE activities".</x:v>
+      </x:c>
+      <x:c r="B2" s="462" t="str">
+        <x:v>This section needs 2 pages — continued from tab "Cassette VAVE activities".</x:v>
+      </x:c>
+      <x:c r="C2" s="462" t="str">
+        <x:v>This section needs 2 pages — continued from tab "Cassette VAVE activities".</x:v>
+      </x:c>
+      <x:c r="D2" s="462" t="str">
+        <x:v>This section needs 2 pages — continued from tab "Cassette VAVE activities".</x:v>
+      </x:c>
+      <x:c r="E2" s="462" t="str">
+        <x:v>This section needs 2 pages — continued from tab "Cassette VAVE activities".</x:v>
+      </x:c>
+      <x:c r="F2" s="462" t="str">
+        <x:v>This section needs 2 pages — continued from tab "Cassette VAVE activities".</x:v>
+      </x:c>
+      <x:c r="G2" s="462" t="str">
+        <x:v>This section needs 2 pages — continued from tab "Cassette VAVE activities".</x:v>
+      </x:c>
+      <x:c r="H2" s="462" t="str">
+        <x:v>This section needs 2 pages — continued from tab "Cassette VAVE activities".</x:v>
+      </x:c>
+      <x:c r="I2" s="462" t="str">
+        <x:v>This section needs 2 pages — continued from tab "Cassette VAVE activities".</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
-      <x:c r="A3" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Case VAVE activities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H3" s="33" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Total:</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I3" s="34" t="n">
-        <x:f>SUMIFS('VAVE-MB 2.0 VAVE Data'!$K$2:$K$21,'VAVE-MB 2.0 VAVE Data'!$C$2:$C$21,"Case VAVE activities",'VAVE-MB 2.0 VAVE Data'!$O$2:$O$21,1)</x:f>
-        <x:v>74.52</x:v>
+      <x:c r="A3" s="456" t="str">
+        <x:v>Cassette VAVE activities · 2 of 2</x:v>
+      </x:c>
+      <x:c r="B3" s="456" t="str">
+        <x:v>Cassette VAVE activities · 2 of 2</x:v>
+      </x:c>
+      <x:c r="C3" s="456" t="str">
+        <x:v>Cassette VAVE activities · 2 of 2</x:v>
+      </x:c>
+      <x:c r="D3" s="456" t="str">
+        <x:v>Cassette VAVE activities · 2 of 2</x:v>
+      </x:c>
+      <x:c r="E3" s="456" t="str">
+        <x:v>Cassette VAVE activities · 2 of 2</x:v>
+      </x:c>
+      <x:c r="F3" s="456" t="str">
+        <x:v>Cassette VAVE activities · 2 of 2</x:v>
+      </x:c>
+      <x:c r="G3" s="456" t="str">
+        <x:v>Cassette VAVE activities · 2 of 2</x:v>
+      </x:c>
+      <x:c r="H3" s="457" t="str">
+        <x:v>Total:</x:v>
+      </x:c>
+      <x:c r="I3" s="459" t="n">
+        <x:f>SUMIFS('VAVE-MB 2.0 VAVE Data'!$K$2:$K$26,'VAVE-MB 2.0 VAVE Data'!$C$2:$C$26,"Cassette VAVE activities",'VAVE-MB 2.0 VAVE Data'!$O$2:$O$26,1)</x:f>
+        <x:v>283.2</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Task Name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="35" t="n"/>
-      <x:c r="C5" s="35" t="n"/>
-      <x:c r="D5" s="35" t="n"/>
-      <x:c r="E5" s="35" t="n"/>
-      <x:c r="F5" s="35" t="n"/>
-      <x:c r="G5" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savings</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">End</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I5" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Status</x:t>
-        </x:is>
+      <x:c r="A5" s="465" t="str">
+        <x:v>Task Name</x:v>
+      </x:c>
+      <x:c r="B5" s="466" t="str">
+        <x:v>Savings</x:v>
+      </x:c>
+      <x:c r="C5" s="466" t="str">
+        <x:v>End</x:v>
+      </x:c>
+      <x:c r="D5" s="466" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5" s="465" t="str">
+        <x:v>Task Name</x:v>
+      </x:c>
+      <x:c r="G5" s="466" t="str">
+        <x:v>Savings</x:v>
+      </x:c>
+      <x:c r="H5" s="466" t="str">
+        <x:v>End</x:v>
+      </x:c>
+      <x:c r="I5" s="466" t="str">
+        <x:v>Status</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="39" customHeight="1">
-      <x:c r="A6" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Plastic Deck Pans</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="36" t="n"/>
-      <x:c r="C6" s="36" t="n"/>
-      <x:c r="D6" s="36" t="n"/>
-      <x:c r="E6" s="36" t="n"/>
-      <x:c r="F6" s="36" t="n"/>
-      <x:c r="G6" s="24" t="n">
-        <x:v>26.65</x:v>
-      </x:c>
-      <x:c r="H6" s="25" t="n">
-        <x:v>46267</x:v>
-      </x:c>
-      <x:c r="I6" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
+      <x:c r="A6" s="470" t="str">
+        <x:v>Pallet - CArdboard design</x:v>
+      </x:c>
+      <x:c r="B6" s="473" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C6" s="475" t="n">
+        <x:v>46307</x:v>
+      </x:c>
+      <x:c r="D6" s="478" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6" s="470" t="str">
+        <x:v>New HP Switch- Danfoss</x:v>
+      </x:c>
+      <x:c r="G6" s="473" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H6" s="475" t="n">
+        <x:v>46314</x:v>
+      </x:c>
+      <x:c r="I6" s="490" t="str">
+        <x:v>Not Started</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="39" customHeight="1">
-      <x:c r="A7" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Simplify Raceway</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G7" s="28" t="n">
-        <x:v>3.07</x:v>
-      </x:c>
-      <x:c r="H7" s="29" t="n">
-        <x:v>46241</x:v>
-      </x:c>
-      <x:c r="I7" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
+      <x:c r="A7" s="482" t="str">
+        <x:v>Remove distributor from LT cassette</x:v>
+      </x:c>
+      <x:c r="B7" s="485" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C7" s="487" t="n">
+        <x:v>46308</x:v>
+      </x:c>
+      <x:c r="D7" s="490" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="E7"/>
+      <x:c r="F7" s="482" t="str">
+        <x:v>Condenser coil with no quoting - Dunan</x:v>
+      </x:c>
+      <x:c r="G7" s="485" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="487" t="n">
+        <x:v>46315</x:v>
+      </x:c>
+      <x:c r="I7" s="490" t="str">
+        <x:v>Not Started</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="39" customHeight="1">
-      <x:c r="A8" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Case power cord</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="36" t="n"/>
-      <x:c r="C8" s="36" t="n"/>
-      <x:c r="D8" s="36" t="n"/>
-      <x:c r="E8" s="36" t="n"/>
-      <x:c r="F8" s="36" t="n"/>
-      <x:c r="G8" s="24" t="n">
-        <x:v>5.5</x:v>
-      </x:c>
-      <x:c r="H8" s="25" t="n">
-        <x:v>46266</x:v>
-      </x:c>
-      <x:c r="I8" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
+      <x:c r="A8" s="470" t="str">
+        <x:v>New plastic base injection foam</x:v>
+      </x:c>
+      <x:c r="B8" s="473" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C8" s="475" t="n">
+        <x:v>46309</x:v>
+      </x:c>
+      <x:c r="D8" s="490" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="E8"/>
+      <x:c r="F8" s="470" t="str">
+        <x:v>Tariff - MT</x:v>
+      </x:c>
+      <x:c r="G8" s="473" t="n">
+        <x:v>43.7</x:v>
+      </x:c>
+      <x:c r="H8" s="475" t="n">
+        <x:v>46188</x:v>
+      </x:c>
+      <x:c r="I8" s="493" t="str">
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="39" customHeight="1">
-      <x:c r="A9" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10Amp Breaker</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G9" s="28" t="n">
-        <x:v>32.5</x:v>
-      </x:c>
-      <x:c r="H9" s="29" t="n">
-        <x:v>46245</x:v>
-      </x:c>
-      <x:c r="I9" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
+      <x:c r="A9" s="482" t="str">
+        <x:v>New TXV Danfoss</x:v>
+      </x:c>
+      <x:c r="B9" s="485" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C9" s="487" t="n">
+        <x:v>46310</x:v>
+      </x:c>
+      <x:c r="D9" s="490" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="E9"/>
+      <x:c r="F9" s="482" t="str">
+        <x:v>Tariff - LT</x:v>
+      </x:c>
+      <x:c r="G9" s="485" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="487" t="n">
+        <x:v>46188</x:v>
+      </x:c>
+      <x:c r="I9" s="493" t="str">
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="39" customHeight="1">
-      <x:c r="A10" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Simplify Under Door Support</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" s="36" t="n"/>
-      <x:c r="C10" s="36" t="n"/>
-      <x:c r="D10" s="36" t="n"/>
-      <x:c r="E10" s="36" t="n"/>
-      <x:c r="F10" s="36" t="n"/>
-      <x:c r="G10" s="24" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="H10" s="25" t="n">
-        <x:v>46241</x:v>
-      </x:c>
-      <x:c r="I10" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="39" customHeight="1">
-      <x:c r="A11" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reduce Qty of Canopy Foam Backers</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G11" s="28" t="n">
-        <x:v>5.3</x:v>
-      </x:c>
-      <x:c r="H11" s="29" t="n">
-        <x:v>46241</x:v>
-      </x:c>
-      <x:c r="I11" s="26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On Track</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A10" s="470" t="str">
+        <x:v>New solenoid Sanhua</x:v>
+      </x:c>
+      <x:c r="B10" s="473" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C10" s="475" t="n">
+        <x:v>46311</x:v>
+      </x:c>
+      <x:c r="D10" s="490" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+      <x:c r="I10"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A11:F11"/>
-    <x:mergeCell ref="A10:F10"/>
+    <x:mergeCell ref="A1:I1"/>
     <x:mergeCell ref="A3:G3"/>
-    <x:mergeCell ref="A5:F5"/>
-    <x:mergeCell ref="A9:F9"/>
-    <x:mergeCell ref="A1:I1"/>
-    <x:mergeCell ref="A8:F8"/>
-    <x:mergeCell ref="A6:F6"/>
-    <x:mergeCell ref="A7:F7"/>
+    <x:mergeCell ref="A2:I2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="00F47C20"/>
+  </x:sheetPr>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="3" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="42" customHeight="1">
+      <x:c r="A1" s="453" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="B1" s="453" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="C1" s="453" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="D1" s="453" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="E1" s="453" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="F1" s="453" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="G1" s="453" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="H1" s="453" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="I1" s="453" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="496" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="B3" s="496" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="C3" s="496" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="D3" s="496" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="E3" s="496" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="F3" s="496" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="G3" s="496" t="str">
+        <x:v>Case VAVE activities</x:v>
+      </x:c>
+      <x:c r="H3" s="497" t="str">
+        <x:v>Total:</x:v>
+      </x:c>
+      <x:c r="I3" s="499" t="n">
+        <x:f>SUMIFS('VAVE-MB 2.0 VAVE Data'!$K$2:$K$26,'VAVE-MB 2.0 VAVE Data'!$C$2:$C$26,"Case VAVE activities",'VAVE-MB 2.0 VAVE Data'!$O$2:$O$26,1)</x:f>
+        <x:v>74.52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="465" t="str">
+        <x:v>Task Name</x:v>
+      </x:c>
+      <x:c r="B5" s="465"/>
+      <x:c r="C5" s="465"/>
+      <x:c r="D5" s="465"/>
+      <x:c r="E5" s="465"/>
+      <x:c r="F5" s="465"/>
+      <x:c r="G5" s="466" t="str">
+        <x:v>Savings</x:v>
+      </x:c>
+      <x:c r="H5" s="466" t="str">
+        <x:v>End</x:v>
+      </x:c>
+      <x:c r="I5" s="466" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="39" customHeight="1">
+      <x:c r="A6" s="470" t="str">
+        <x:v>Plastic Deck Pans</x:v>
+      </x:c>
+      <x:c r="B6" s="470"/>
+      <x:c r="C6" s="470"/>
+      <x:c r="D6" s="470"/>
+      <x:c r="E6" s="470"/>
+      <x:c r="F6" s="470"/>
+      <x:c r="G6" s="473" t="n">
+        <x:v>26.65</x:v>
+      </x:c>
+      <x:c r="H6" s="475" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="I6" s="478" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="39" customHeight="1">
+      <x:c r="A7" s="482" t="str">
+        <x:v>Simplify Raceway</x:v>
+      </x:c>
+      <x:c r="B7" s="482"/>
+      <x:c r="C7" s="482"/>
+      <x:c r="D7" s="482"/>
+      <x:c r="E7" s="482"/>
+      <x:c r="F7" s="482"/>
+      <x:c r="G7" s="485" t="n">
+        <x:v>3.07</x:v>
+      </x:c>
+      <x:c r="H7" s="487" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="I7" s="478" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="39" customHeight="1">
+      <x:c r="A8" s="470" t="str">
+        <x:v>Case power cord</x:v>
+      </x:c>
+      <x:c r="B8" s="470"/>
+      <x:c r="C8" s="470"/>
+      <x:c r="D8" s="470"/>
+      <x:c r="E8" s="470"/>
+      <x:c r="F8" s="470"/>
+      <x:c r="G8" s="473" t="n">
+        <x:v>5.5</x:v>
+      </x:c>
+      <x:c r="H8" s="475" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="I8" s="478" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="39" customHeight="1">
+      <x:c r="A9" s="482" t="str">
+        <x:v>10Amp Breaker</x:v>
+      </x:c>
+      <x:c r="B9" s="482"/>
+      <x:c r="C9" s="482"/>
+      <x:c r="D9" s="482"/>
+      <x:c r="E9" s="482"/>
+      <x:c r="F9" s="482"/>
+      <x:c r="G9" s="485" t="n">
+        <x:v>32.5</x:v>
+      </x:c>
+      <x:c r="H9" s="487" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="I9" s="478" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="39" customHeight="1">
+      <x:c r="A10" s="470" t="str">
+        <x:v>Simplify Under Door Support</x:v>
+      </x:c>
+      <x:c r="B10" s="470"/>
+      <x:c r="C10" s="470"/>
+      <x:c r="D10" s="470"/>
+      <x:c r="E10" s="470"/>
+      <x:c r="F10" s="470"/>
+      <x:c r="G10" s="473" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="H10" s="475" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="I10" s="478" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="39" customHeight="1">
+      <x:c r="A11" s="482" t="str">
+        <x:v>Reduce Qty of Canopy Foam Backers</x:v>
+      </x:c>
+      <x:c r="B11" s="482"/>
+      <x:c r="C11" s="482"/>
+      <x:c r="D11" s="482"/>
+      <x:c r="E11" s="482"/>
+      <x:c r="F11" s="482"/>
+      <x:c r="G11" s="485" t="n">
+        <x:v>5.3</x:v>
+      </x:c>
+      <x:c r="H11" s="487" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="I11" s="478" t="str">
+        <x:v>On Track</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:I1"/>
+    <x:mergeCell ref="A3:G3"/>
+    <x:mergeCell ref="A5:F5"/>
+    <x:mergeCell ref="A6:F6"/>
+    <x:mergeCell ref="A7:F7"/>
+    <x:mergeCell ref="A8:F8"/>
+    <x:mergeCell ref="A9:F9"/>
+    <x:mergeCell ref="A10:F10"/>
+    <x:mergeCell ref="A11:F11"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -14686,11 +16386,32 @@
         <x:v>Automatic layout: 1–7 rows = single column; 8–14 rows = two columns; more than 14 rows = continuation slides.</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" ht="30" customHeight="1">
+      <x:c r="A15" s="500" t="str">
+        <x:v>Last refreshed from DG-PH2-6-25.vpmt. Re-run Generate VAVE Slides.cmd after saving tracker changes.</x:v>
+      </x:c>
+      <x:c r="B15" s="500" t="str">
+        <x:v>Last refreshed from DG-PH2-6-25.vpmt. Re-run Generate VAVE Slides.cmd after saving tracker changes.</x:v>
+      </x:c>
+      <x:c r="C15" s="500" t="str">
+        <x:v>Last refreshed from DG-PH2-6-25.vpmt. Re-run Generate VAVE Slides.cmd after saving tracker changes.</x:v>
+      </x:c>
+      <x:c r="D15" s="500" t="str">
+        <x:v>Last refreshed from DG-PH2-6-25.vpmt. Re-run Generate VAVE Slides.cmd after saving tracker changes.</x:v>
+      </x:c>
+      <x:c r="E15" s="500" t="str">
+        <x:v>Last refreshed from DG-PH2-6-25.vpmt. Re-run Generate VAVE Slides.cmd after saving tracker changes.</x:v>
+      </x:c>
+      <x:c r="F15" s="500" t="str">
+        <x:v>Last refreshed from DG-PH2-6-25.vpmt. Re-run Generate VAVE Slides.cmd after saving tracker changes.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A3:F3"/>
     <x:mergeCell ref="A13:F13"/>
+    <x:mergeCell ref="A15:F15"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
